--- a/Excel-XLSX/UN-LAO.xlsx
+++ b/Excel-XLSX/UN-LAO.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>﻿"page"</t>
   </si>
@@ -63,31 +63,136 @@
     <t>asylum_seekers</t>
   </si>
   <si>
-    <t>returned_refugees</t>
-  </si>
-  <si>
     <t>idps</t>
   </si>
   <si>
-    <t>returned_idps</t>
+    <t>oip</t>
   </si>
   <si>
     <t>stateless</t>
   </si>
   <si>
+    <t>hst</t>
+  </si>
+  <si>
     <t>ooc</t>
   </si>
   <si>
-    <t>oip</t>
-  </si>
-  <si>
-    <t>hst</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>y6Y3Zr</t>
+    <t>4CRaa9</t>
+  </si>
+  <si>
+    <t>1976</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>CAM</t>
+  </si>
+  <si>
+    <t>KHM</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Lao People's Dem. Rep.</t>
+  </si>
+  <si>
+    <t>LAO</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1977</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1980</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>3500</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1983</t>
+  </si>
+  <si>
+    <t>1260</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1987</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>1972</t>
@@ -105,25 +210,10 @@
     <t>MMR</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>Lao People's Dem. Rep.</t>
-  </si>
-  <si>
-    <t>LAO</t>
-  </si>
-  <si>
     <t>700</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>12</t>
   </si>
   <si>
     <t>1975</t>
@@ -142,111 +232,6 @@
   </si>
   <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1976</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Cambodia</t>
-  </si>
-  <si>
-    <t>CAM</t>
-  </si>
-  <si>
-    <t>KHM</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1977</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1978</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1980</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>19940</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1981</t>
-  </si>
-  <si>
-    <t>3500</t>
-  </si>
-  <si>
-    <t>6900</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1982</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1983</t>
-  </si>
-  <si>
-    <t>1260</t>
-  </si>
-  <si>
-    <t>2240</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1984</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1987</t>
-  </si>
-  <si>
-    <t>80</t>
   </si>
 </sst>
 </file>
@@ -631,7 +616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <sheetData>
     <row r="1">
@@ -695,827 +680,749 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="R2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="O3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="O5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="O7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="O8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Excel-XLSX/UN-LAO.xlsx
+++ b/Excel-XLSX/UN-LAO.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>﻿"page"</t>
   </si>
@@ -63,25 +63,31 @@
     <t>asylum_seekers</t>
   </si>
   <si>
+    <t>returned_refugees</t>
+  </si>
+  <si>
     <t>idps</t>
   </si>
   <si>
+    <t>returned_idps</t>
+  </si>
+  <si>
+    <t>stateless</t>
+  </si>
+  <si>
+    <t>ooc</t>
+  </si>
+  <si>
     <t>oip</t>
   </si>
   <si>
-    <t>stateless</t>
-  </si>
-  <si>
     <t>hst</t>
   </si>
   <si>
-    <t>ooc</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>4CRaa9</t>
+    <t>dl2k5M</t>
   </si>
   <si>
     <t>1976</t>
@@ -150,6 +156,9 @@
     <t>10370</t>
   </si>
   <si>
+    <t>19940</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -159,6 +168,9 @@
     <t>3500</t>
   </si>
   <si>
+    <t>6900</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -172,6 +184,9 @@
   </si>
   <si>
     <t>1260</t>
+  </si>
+  <si>
+    <t>2240</t>
   </si>
   <si>
     <t>9</t>
@@ -616,7 +631,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <sheetData>
     <row r="1">
@@ -680,749 +695,827 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>31</v>
+      <c r="V3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>32</v>
+        <v>56</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
